--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="plot_terms" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="plot_terms"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -55,64 +55,64 @@
     <t>N</t>
   </si>
   <si>
+    <t>pre test - resistance</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>resistance</t>
+  </si>
+  <si>
+    <t>pre test</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>resistance - resistance - value</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>resistance - resistance - min</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>pre test - resistance</t>
-  </si>
-  <si>
     <t>pre test - isp</t>
   </si>
   <si>
+    <t>isp</t>
+  </si>
+  <si>
+    <t>isp - isp - value</t>
+  </si>
+  <si>
+    <t>isp - isp - min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>isp - isp - max</t>
+  </si>
+  <si>
     <t>pre test - Thrust</t>
   </si>
   <si>
+    <t>Thrust</t>
+  </si>
+  <si>
+    <t>Thrust - Thrust - value</t>
+  </si>
+  <si>
     <t>post test - Thrust</t>
   </si>
   <si>
-    <t>SN</t>
-  </si>
-  <si>
-    <t>resistance</t>
-  </si>
-  <si>
-    <t>isp</t>
-  </si>
-  <si>
-    <t>Thrust</t>
-  </si>
-  <si>
-    <t>pre test</t>
-  </si>
-  <si>
     <t>post test</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>max</t>
-  </si>
-  <si>
-    <t>resistance - resistance - value</t>
-  </si>
-  <si>
-    <t>resistance - resistance - min</t>
-  </si>
-  <si>
-    <t>isp - isp - value</t>
-  </si>
-  <si>
-    <t>isp - isp - min</t>
-  </si>
-  <si>
-    <t>isp - isp - max</t>
-  </si>
-  <si>
-    <t>Thrust - Thrust - value</t>
   </si>
   <si>
     <t>Thrust - Thrust - min</t>
@@ -124,8 +124,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,10 +137,15 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -150,7 +156,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -160,34 +166,64 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="8">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -196,10 +232,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -237,69 +273,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -323,54 +361,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -380,7 +417,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -389,7 +426,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -398,7 +435,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -406,10 +443,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -438,7 +475,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -451,13 +488,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -475,18 +511,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="33.7109375" customWidth="1"/>
+    <col min="1" max="1" style="6" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="23.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="19.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="7" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="7" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="6" width="33.71928571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -514,242 +560,263 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I3" s="3"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>8</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="I5" s="3"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
+      <c r="I8" s="3"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>8</v>
-      </c>
-      <c r="L4" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="F9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="I9" s="3"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="3" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A10">
-      <formula1>",Y,N"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D10">
-      <formula1>"SN,Program,Space Vehicle"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>Plot?</t>
   </si>
@@ -49,28 +49,25 @@
     <t>Series Label</t>
   </si>
   <si>
-    <t>Pre Test Functional - Specific Impulse</t>
-  </si>
-  <si>
-    <t>Pre Test Functional - Resistance</t>
+    <t>isp - Pre Test Functional</t>
+  </si>
+  <si>
+    <t>resistance - Pre Test Functional</t>
   </si>
   <si>
     <t>SN</t>
   </si>
   <si>
+    <t>isp</t>
+  </si>
+  <si>
+    <t>resistance</t>
+  </si>
+  <si>
     <t>Pre Test Functional</t>
   </si>
   <si>
-    <t>Specific Impulse</t>
-  </si>
-  <si>
-    <t>Resistance</t>
-  </si>
-  <si>
     <t>40.0</t>
-  </si>
-  <si>
-    <t>5.0</t>
   </si>
   <si>
     <t>44.0</t>
@@ -435,12 +432,11 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
     <col min="7" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="40.7109375" customWidth="1"/>
+    <col min="11" max="11" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -489,13 +485,13 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -509,12 +505,15 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
         <v>18</v>
       </c>
       <c r="K3" t="s">

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="75">
   <si>
     <t>Plot?</t>
   </si>
@@ -49,28 +49,196 @@
     <t>Series Label</t>
   </si>
   <si>
-    <t>isp - Pre Test Functional</t>
-  </si>
-  <si>
-    <t>resistance - Pre Test Functional</t>
+    <t>Program Name - Document Profile</t>
+  </si>
+  <si>
+    <t>Serial Number - Document Profile</t>
+  </si>
+  <si>
+    <t>Date Compiled - Document Profile</t>
+  </si>
+  <si>
+    <t>Source Bundle Path - Document Profile</t>
+  </si>
+  <si>
+    <t>Ignition Delay Measured - Functional Acceptance</t>
+  </si>
+  <si>
+    <t>Chamber Pressure Over - Functional Acceptance</t>
+  </si>
+  <si>
+    <t>Harness Resistance - Functional Acceptance</t>
+  </si>
+  <si>
+    <t>Leak Check Missing - Functional Acceptance</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Value - Performance KPI</t>
+  </si>
+  <si>
+    <t>Power Draw Idle - Performance KPI</t>
+  </si>
+  <si>
+    <t>Power Draw Peak - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thermal Margin Low - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Temp - Environmental</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Status - Environmental</t>
+  </si>
+  <si>
+    <t>Random Vib Z Amplitude - Environmental</t>
+  </si>
+  <si>
+    <t>TC-02 Post Trim - Calibration</t>
+  </si>
+  <si>
+    <t>LVDT-2 Status - Calibration</t>
+  </si>
+  <si>
+    <t>Calibration Workbook Sheets - Attachment Index</t>
   </si>
   <si>
     <t>SN</t>
   </si>
   <si>
-    <t>isp</t>
-  </si>
-  <si>
-    <t>resistance</t>
-  </si>
-  <si>
-    <t>Pre Test Functional</t>
-  </si>
-  <si>
-    <t>40.0</t>
-  </si>
-  <si>
-    <t>44.0</t>
+    <t>Program Name</t>
+  </si>
+  <si>
+    <t>Serial Number</t>
+  </si>
+  <si>
+    <t>Date Compiled</t>
+  </si>
+  <si>
+    <t>Source Bundle Path</t>
+  </si>
+  <si>
+    <t>Ignition Delay Measured</t>
+  </si>
+  <si>
+    <t>Chamber Pressure Over</t>
+  </si>
+  <si>
+    <t>Harness Resistance</t>
+  </si>
+  <si>
+    <t>Leak Check Missing</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Value</t>
+  </si>
+  <si>
+    <t>Power Draw Idle</t>
+  </si>
+  <si>
+    <t>Power Draw Peak</t>
+  </si>
+  <si>
+    <t>Thermal Margin Low</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Temp</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Status</t>
+  </si>
+  <si>
+    <t>Random Vib Z Amplitude</t>
+  </si>
+  <si>
+    <t>TC-02 Post Trim</t>
+  </si>
+  <si>
+    <t>LVDT-2 Status</t>
+  </si>
+  <si>
+    <t>Calibration Workbook Sheets</t>
+  </si>
+  <si>
+    <t>Document Profile</t>
+  </si>
+  <si>
+    <t>Functional Acceptance</t>
+  </si>
+  <si>
+    <t>Performance KPI</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>Calibration</t>
+  </si>
+  <si>
+    <t>Attachment Index</t>
+  </si>
+  <si>
+    <t>175.0</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>75.0</t>
+  </si>
+  <si>
+    <t>140.0</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>90.0</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>12.0</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>195.0</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>1e-05</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>95.0</t>
+  </si>
+  <si>
+    <t>155.0</t>
+  </si>
+  <si>
+    <t>100.0</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>1.004</t>
   </si>
 </sst>
 </file>
@@ -428,15 +596,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="49.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" customWidth="1"/>
     <col min="7" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="34.7109375" customWidth="1"/>
+    <col min="11" max="11" width="49.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -479,19 +648,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -502,30 +665,374 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="4" spans="1:11">
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" t="s">
+        <v>72</v>
+      </c>
+      <c r="K14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" t="s">
+        <v>73</v>
+      </c>
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19" t="s">
+        <v>64</v>
+      </c>
+      <c r="K19" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A20">
       <formula1>",Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D20">
       <formula1>"SN,Program,Space Vehicle"</formula1>
     </dataValidation>
   </dataValidations>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
   <si>
     <t>Plot?</t>
   </si>
@@ -70,39 +70,39 @@
     <t>Harness Resistance - Functional Acceptance</t>
   </si>
   <si>
+    <t>Thrust Nominal Value - Performance KPI</t>
+  </si>
+  <si>
+    <t>Power Draw Idle - Performance KPI</t>
+  </si>
+  <si>
+    <t>Power Draw Peak - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thermal Margin Low - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Temp - Environmental</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Status - Environmental</t>
+  </si>
+  <si>
+    <t>Random Vib Z Amplitude - Environmental</t>
+  </si>
+  <si>
+    <t>TC-02 Post Trim - Calibration</t>
+  </si>
+  <si>
+    <t>LVDT-2 Status - Calibration</t>
+  </si>
+  <si>
+    <t>Calibration Workbook Sheets - Attachment Index</t>
+  </si>
+  <si>
     <t>Leak Check Missing - Functional Acceptance</t>
   </si>
   <si>
-    <t>Thrust Nominal Value - Performance KPI</t>
-  </si>
-  <si>
-    <t>Power Draw Idle - Performance KPI</t>
-  </si>
-  <si>
-    <t>Power Draw Peak - Performance KPI</t>
-  </si>
-  <si>
-    <t>Thermal Margin Low - Performance KPI</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Temp - Environmental</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Status - Environmental</t>
-  </si>
-  <si>
-    <t>Random Vib Z Amplitude - Environmental</t>
-  </si>
-  <si>
-    <t>TC-02 Post Trim - Calibration</t>
-  </si>
-  <si>
-    <t>LVDT-2 Status - Calibration</t>
-  </si>
-  <si>
-    <t>Calibration Workbook Sheets - Attachment Index</t>
-  </si>
-  <si>
     <t>SN</t>
   </si>
   <si>
@@ -127,39 +127,39 @@
     <t>Harness Resistance</t>
   </si>
   <si>
+    <t>Thrust Nominal Value</t>
+  </si>
+  <si>
+    <t>Power Draw Idle</t>
+  </si>
+  <si>
+    <t>Power Draw Peak</t>
+  </si>
+  <si>
+    <t>Thermal Margin Low</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Temp</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Status</t>
+  </si>
+  <si>
+    <t>Random Vib Z Amplitude</t>
+  </si>
+  <si>
+    <t>TC-02 Post Trim</t>
+  </si>
+  <si>
+    <t>LVDT-2 Status</t>
+  </si>
+  <si>
+    <t>Calibration Workbook Sheets</t>
+  </si>
+  <si>
     <t>Leak Check Missing</t>
   </si>
   <si>
-    <t>Thrust Nominal Value</t>
-  </si>
-  <si>
-    <t>Power Draw Idle</t>
-  </si>
-  <si>
-    <t>Power Draw Peak</t>
-  </si>
-  <si>
-    <t>Thermal Margin Low</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Temp</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Status</t>
-  </si>
-  <si>
-    <t>Random Vib Z Amplitude</t>
-  </si>
-  <si>
-    <t>TC-02 Post Trim</t>
-  </si>
-  <si>
-    <t>LVDT-2 Status</t>
-  </si>
-  <si>
-    <t>Calibration Workbook Sheets</t>
-  </si>
-  <si>
     <t>Document Profile</t>
   </si>
   <si>
@@ -178,6 +178,18 @@
     <t>Attachment Index</t>
   </si>
   <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>psia</t>
+  </si>
+  <si>
+    <t>ω</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
     <t>175.0</t>
   </si>
   <si>
@@ -208,9 +220,6 @@
     <t>0.005</t>
   </si>
   <si>
-    <t>4.0</t>
-  </si>
-  <si>
     <t>0.85</t>
   </si>
   <si>
@@ -220,25 +229,25 @@
     <t>5.3</t>
   </si>
   <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>95.0</t>
+  </si>
+  <si>
+    <t>155.0</t>
+  </si>
+  <si>
+    <t>100.0</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>1.004</t>
+  </si>
+  <si>
     <t>1e-05</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>95.0</t>
-  </si>
-  <si>
-    <t>155.0</t>
-  </si>
-  <si>
-    <t>100.0</t>
-  </si>
-  <si>
-    <t>1.01</t>
-  </si>
-  <si>
-    <t>1.004</t>
   </si>
 </sst>
 </file>
@@ -690,6 +699,12 @@
       <c r="F4" t="s">
         <v>48</v>
       </c>
+      <c r="H4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" t="s">
+        <v>57</v>
+      </c>
       <c r="K4" t="s">
         <v>13</v>
       </c>
@@ -724,8 +739,14 @@
       <c r="F6" t="s">
         <v>49</v>
       </c>
+      <c r="G6" t="s">
+        <v>54</v>
+      </c>
       <c r="I6" t="s">
-        <v>65</v>
+        <v>68</v>
+      </c>
+      <c r="J6" t="s">
+        <v>54</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -744,11 +765,17 @@
       <c r="F7" t="s">
         <v>49</v>
       </c>
+      <c r="G7" t="s">
+        <v>55</v>
+      </c>
       <c r="H7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="J7" t="s">
+        <v>55</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -767,11 +794,17 @@
       <c r="F8" t="s">
         <v>49</v>
       </c>
+      <c r="G8" t="s">
+        <v>56</v>
+      </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I8" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="J8" t="s">
+        <v>56</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -788,10 +821,13 @@
         <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="H9" t="s">
+        <v>59</v>
       </c>
       <c r="I9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -811,10 +847,10 @@
         <v>50</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -834,10 +870,10 @@
         <v>50</v>
       </c>
       <c r="H11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -857,10 +893,10 @@
         <v>50</v>
       </c>
       <c r="H12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -877,13 +913,13 @@
         <v>41</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -903,7 +939,7 @@
         <v>51</v>
       </c>
       <c r="H14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I14" t="s">
         <v>72</v>
@@ -926,10 +962,10 @@
         <v>51</v>
       </c>
       <c r="H15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I15" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -946,13 +982,13 @@
         <v>44</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I16" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -972,10 +1008,10 @@
         <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K17" t="s">
         <v>26</v>
@@ -992,13 +1028,13 @@
         <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H18" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I18" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K18" t="s">
         <v>27</v>
@@ -1015,13 +1051,10 @@
         <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="I19" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
   <si>
     <t>Plot?</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Source Bundle Path - Document Profile</t>
   </si>
   <si>
-    <t>Ignition Delay Measured - Functional Acceptance</t>
-  </si>
-  <si>
     <t>Chamber Pressure Over - Functional Acceptance</t>
   </si>
   <si>
@@ -73,18 +70,12 @@
     <t>Thrust Nominal Value - Performance KPI</t>
   </si>
   <si>
-    <t>Power Draw Idle - Performance KPI</t>
-  </si>
-  <si>
     <t>Power Draw Peak - Performance KPI</t>
   </si>
   <si>
     <t>Thermal Margin Low - Performance KPI</t>
   </si>
   <si>
-    <t>Thermal Soak High Temp - Environmental</t>
-  </si>
-  <si>
     <t>Thermal Soak High Status - Environmental</t>
   </si>
   <si>
@@ -100,9 +91,6 @@
     <t>Calibration Workbook Sheets - Attachment Index</t>
   </si>
   <si>
-    <t>Leak Check Missing - Functional Acceptance</t>
-  </si>
-  <si>
     <t>SN</t>
   </si>
   <si>
@@ -118,9 +106,6 @@
     <t>Source Bundle Path</t>
   </si>
   <si>
-    <t>Ignition Delay Measured</t>
-  </si>
-  <si>
     <t>Chamber Pressure Over</t>
   </si>
   <si>
@@ -130,18 +115,12 @@
     <t>Thrust Nominal Value</t>
   </si>
   <si>
-    <t>Power Draw Idle</t>
-  </si>
-  <si>
     <t>Power Draw Peak</t>
   </si>
   <si>
     <t>Thermal Margin Low</t>
   </si>
   <si>
-    <t>Thermal Soak High Temp</t>
-  </si>
-  <si>
     <t>Thermal Soak High Status</t>
   </si>
   <si>
@@ -157,9 +136,6 @@
     <t>Calibration Workbook Sheets</t>
   </si>
   <si>
-    <t>Leak Check Missing</t>
-  </si>
-  <si>
     <t>Document Profile</t>
   </si>
   <si>
@@ -178,15 +154,15 @@
     <t>Attachment Index</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>psia</t>
   </si>
   <si>
     <t>ω</t>
   </si>
   <si>
+    <t>sheets</t>
+  </si>
+  <si>
     <t>4.0</t>
   </si>
   <si>
@@ -196,18 +172,12 @@
     <t>4.8</t>
   </si>
   <si>
-    <t>75.0</t>
-  </si>
-  <si>
     <t>140.0</t>
   </si>
   <si>
     <t>8.0</t>
   </si>
   <si>
-    <t>90.0</t>
-  </si>
-  <si>
     <t>1.5</t>
   </si>
   <si>
@@ -220,9 +190,6 @@
     <t>0.005</t>
   </si>
   <si>
-    <t>0.85</t>
-  </si>
-  <si>
     <t>195.0</t>
   </si>
   <si>
@@ -232,22 +199,16 @@
     <t>5.5</t>
   </si>
   <si>
+    <t>155.0</t>
+  </si>
+  <si>
     <t>95.0</t>
   </si>
   <si>
-    <t>155.0</t>
-  </si>
-  <si>
-    <t>100.0</t>
-  </si>
-  <si>
     <t>1.01</t>
   </si>
   <si>
     <t>1.004</t>
-  </si>
-  <si>
-    <t>1e-05</t>
   </si>
 </sst>
 </file>
@@ -605,16 +566,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" customWidth="1"/>
+    <col min="2" max="2" width="48.7109375" customWidth="1"/>
     <col min="3" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="29.7109375" customWidth="1"/>
     <col min="6" max="6" width="23.7109375" customWidth="1"/>
     <col min="7" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="49.7109375" customWidth="1"/>
+    <col min="11" max="11" width="48.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -657,13 +618,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -674,13 +635,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -691,19 +652,19 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="K4" t="s">
         <v>13</v>
@@ -714,13 +675,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
@@ -731,22 +692,25 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>46</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="J6" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -757,25 +721,25 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J7" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -786,25 +750,19 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
-      </c>
-      <c r="J8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -815,19 +773,19 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -838,19 +796,19 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -861,19 +819,19 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="I11" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -884,19 +842,19 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H12" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I12" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -907,19 +865,19 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" t="s">
         <v>63</v>
-      </c>
-      <c r="I13" t="s">
-        <v>74</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -930,19 +888,19 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" t="s">
         <v>64</v>
-      </c>
-      <c r="I14" t="s">
-        <v>72</v>
       </c>
       <c r="K14" t="s">
         <v>23</v>
@@ -953,119 +911,36 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="G15" t="s">
+        <v>48</v>
       </c>
       <c r="H15" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="I15" t="s">
-        <v>65</v>
+        <v>49</v>
+      </c>
+      <c r="J15" t="s">
+        <v>48</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="B16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I16" t="s">
-        <v>75</v>
-      </c>
-      <c r="K16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11">
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H17" t="s">
-        <v>67</v>
-      </c>
-      <c r="I17" t="s">
-        <v>76</v>
-      </c>
-      <c r="K17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11">
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" t="s">
-        <v>57</v>
-      </c>
-      <c r="I18" t="s">
-        <v>57</v>
-      </c>
-      <c r="K18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11">
-      <c r="B19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" t="s">
-        <v>49</v>
-      </c>
-      <c r="I19" t="s">
-        <v>77</v>
-      </c>
-      <c r="K19" t="s">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A16">
       <formula1>",Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D16">
       <formula1>"SN,Program,Space Vehicle"</formula1>
     </dataValidation>
   </dataValidations>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="61">
   <si>
     <t>Plot?</t>
   </si>
@@ -88,9 +88,6 @@
     <t>LVDT-2 Status - Calibration</t>
   </si>
   <si>
-    <t>Calibration Workbook Sheets - Attachment Index</t>
-  </si>
-  <si>
     <t>SN</t>
   </si>
   <si>
@@ -133,9 +130,6 @@
     <t>LVDT-2 Status</t>
   </si>
   <si>
-    <t>Calibration Workbook Sheets</t>
-  </si>
-  <si>
     <t>Document Profile</t>
   </si>
   <si>
@@ -151,16 +145,10 @@
     <t>Calibration</t>
   </si>
   <si>
-    <t>Attachment Index</t>
-  </si>
-  <si>
     <t>psia</t>
   </si>
   <si>
     <t>ω</t>
-  </si>
-  <si>
-    <t>sheets</t>
   </si>
   <si>
     <t>4.0</t>
@@ -566,16 +554,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="48.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.7109375" customWidth="1"/>
     <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" customWidth="1"/>
     <col min="6" max="6" width="23.7109375" customWidth="1"/>
     <col min="7" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="48.7109375" customWidth="1"/>
+    <col min="11" max="11" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -618,13 +606,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -635,13 +623,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -652,19 +640,19 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K4" t="s">
         <v>13</v>
@@ -675,13 +663,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
@@ -692,25 +680,25 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" t="s">
         <v>46</v>
       </c>
-      <c r="H6" t="s">
-        <v>50</v>
-      </c>
       <c r="I6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -721,25 +709,25 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
         <v>47</v>
       </c>
-      <c r="H7" t="s">
-        <v>51</v>
-      </c>
       <c r="I7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -750,19 +738,19 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -773,19 +761,19 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -796,19 +784,19 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -819,19 +807,19 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -842,19 +830,19 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -865,19 +853,19 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -888,59 +876,30 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="K14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" t="s">
-        <v>48</v>
-      </c>
-      <c r="H15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" t="s">
-        <v>49</v>
-      </c>
-      <c r="J15" t="s">
-        <v>48</v>
-      </c>
-      <c r="K15" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15">
       <formula1>",Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D15">
       <formula1>"SN,Program,Space Vehicle"</formula1>
     </dataValidation>
   </dataValidations>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="75">
   <si>
     <t>Plot?</t>
   </si>
@@ -64,21 +64,39 @@
     <t>Chamber Pressure Over - Functional Acceptance</t>
   </si>
   <si>
+    <t>Chamber Pressure Units - Functional Acceptance</t>
+  </si>
+  <si>
     <t>Harness Resistance - Functional Acceptance</t>
   </si>
   <si>
+    <t>Harness Resistance Quality - Functional Acceptance</t>
+  </si>
+  <si>
     <t>Thrust Nominal Value - Performance KPI</t>
   </si>
   <si>
+    <t>Thrust Nominal Target</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Confidence - Performance KPI</t>
+  </si>
+  <si>
     <t>Power Draw Peak - Performance KPI</t>
   </si>
   <si>
+    <t>Power Draw Peak Source - Performance KPI</t>
+  </si>
+  <si>
     <t>Thermal Margin Low - Performance KPI</t>
   </si>
   <si>
     <t>Thermal Soak High Status - Environmental</t>
   </si>
   <si>
+    <t>Thermal Soak High Duration - Environmental</t>
+  </si>
+  <si>
     <t>Random Vib Z Amplitude - Environmental</t>
   </si>
   <si>
@@ -106,21 +124,36 @@
     <t>Chamber Pressure Over</t>
   </si>
   <si>
+    <t>Chamber Pressure Units</t>
+  </si>
+  <si>
     <t>Harness Resistance</t>
   </si>
   <si>
+    <t>Harness Resistance Quality</t>
+  </si>
+  <si>
     <t>Thrust Nominal Value</t>
   </si>
   <si>
+    <t>Thrust Nominal Confidence</t>
+  </si>
+  <si>
     <t>Power Draw Peak</t>
   </si>
   <si>
+    <t>Power Draw Peak Source</t>
+  </si>
+  <si>
     <t>Thermal Margin Low</t>
   </si>
   <si>
     <t>Thermal Soak High Status</t>
   </si>
   <si>
+    <t>Thermal Soak High Duration</t>
+  </si>
+  <si>
     <t>Random Vib Z Amplitude</t>
   </si>
   <si>
@@ -157,9 +190,15 @@
     <t>175.0</t>
   </si>
   <si>
+    <t>6.0</t>
+  </si>
+  <si>
     <t>4.8</t>
   </si>
   <si>
+    <t>0.97</t>
+  </si>
+  <si>
     <t>140.0</t>
   </si>
   <si>
@@ -179,6 +218,9 @@
   </si>
   <si>
     <t>195.0</t>
+  </si>
+  <si>
+    <t>201.0</t>
   </si>
   <si>
     <t>5.3</t>
@@ -554,16 +596,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="47.7109375" customWidth="1"/>
+    <col min="2" max="2" width="52.7109375" customWidth="1"/>
     <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
     <col min="6" max="6" width="23.7109375" customWidth="1"/>
     <col min="7" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="47.7109375" customWidth="1"/>
+    <col min="11" max="11" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -606,13 +648,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -623,13 +665,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -640,19 +682,19 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H4" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="K4" t="s">
         <v>13</v>
@@ -663,13 +705,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
@@ -680,25 +722,25 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="H6" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="I6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" t="s">
         <v>54</v>
-      </c>
-      <c r="J6" t="s">
-        <v>43</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -709,25 +751,19 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -738,19 +774,25 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
       </c>
       <c r="H8" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="I8" t="s">
-        <v>56</v>
+        <v>69</v>
+      </c>
+      <c r="J8" t="s">
+        <v>55</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -761,19 +803,13 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -784,19 +820,19 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -807,19 +843,16 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -830,19 +863,19 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -853,19 +886,19 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I13" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -876,30 +909,162 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="K14" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="15" spans="1:11">
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" t="s">
+        <v>62</v>
+      </c>
+      <c r="I15" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" t="s">
+        <v>72</v>
+      </c>
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" t="s">
+        <v>64</v>
+      </c>
+      <c r="K18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A21">
       <formula1>",Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D21">
       <formula1>"SN,Program,Space Vehicle"</formula1>
     </dataValidation>
   </dataValidations>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="77">
   <si>
     <t>Plot?</t>
   </si>
@@ -76,66 +76,72 @@
     <t>Thrust Nominal Value - Performance KPI</t>
   </si>
   <si>
+    <t>Thrust Nominal Target - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Confidence - Performance KPI</t>
+  </si>
+  <si>
+    <t>Power Draw Peak - Performance KPI</t>
+  </si>
+  <si>
+    <t>Power Draw Peak Source - Performance KPI</t>
+  </si>
+  <si>
+    <t>Power Draw Idle Source - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thermal Margin Low - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Status - Environmental</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Duration - Environmental</t>
+  </si>
+  <si>
+    <t>Random Vib Z Amplitude - Environmental</t>
+  </si>
+  <si>
+    <t>TC-02 Post Trim - Calibration</t>
+  </si>
+  <si>
+    <t>LVDT-2 Status - Calibration</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>Program Name</t>
+  </si>
+  <si>
+    <t>Serial Number</t>
+  </si>
+  <si>
+    <t>Date Compiled</t>
+  </si>
+  <si>
+    <t>Source Bundle Path</t>
+  </si>
+  <si>
+    <t>Chamber Pressure Over</t>
+  </si>
+  <si>
+    <t>Chamber Pressure Units</t>
+  </si>
+  <si>
+    <t>Harness Resistance</t>
+  </si>
+  <si>
+    <t>Harness Resistance Quality</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Value</t>
+  </si>
+  <si>
     <t>Thrust Nominal Target</t>
   </si>
   <si>
-    <t>Thrust Nominal Confidence - Performance KPI</t>
-  </si>
-  <si>
-    <t>Power Draw Peak - Performance KPI</t>
-  </si>
-  <si>
-    <t>Power Draw Peak Source - Performance KPI</t>
-  </si>
-  <si>
-    <t>Thermal Margin Low - Performance KPI</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Status - Environmental</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Duration - Environmental</t>
-  </si>
-  <si>
-    <t>Random Vib Z Amplitude - Environmental</t>
-  </si>
-  <si>
-    <t>TC-02 Post Trim - Calibration</t>
-  </si>
-  <si>
-    <t>LVDT-2 Status - Calibration</t>
-  </si>
-  <si>
-    <t>SN</t>
-  </si>
-  <si>
-    <t>Program Name</t>
-  </si>
-  <si>
-    <t>Serial Number</t>
-  </si>
-  <si>
-    <t>Date Compiled</t>
-  </si>
-  <si>
-    <t>Source Bundle Path</t>
-  </si>
-  <si>
-    <t>Chamber Pressure Over</t>
-  </si>
-  <si>
-    <t>Chamber Pressure Units</t>
-  </si>
-  <si>
-    <t>Harness Resistance</t>
-  </si>
-  <si>
-    <t>Harness Resistance Quality</t>
-  </si>
-  <si>
-    <t>Thrust Nominal Value</t>
-  </si>
-  <si>
     <t>Thrust Nominal Confidence</t>
   </si>
   <si>
@@ -145,6 +151,9 @@
     <t>Power Draw Peak Source</t>
   </si>
   <si>
+    <t>Power Draw Idle Source</t>
+  </si>
+  <si>
     <t>Thermal Margin Low</t>
   </si>
   <si>
@@ -194,9 +203,6 @@
   </si>
   <si>
     <t>4.8</t>
-  </si>
-  <si>
-    <t>0.97</t>
   </si>
   <si>
     <t>140.0</t>
@@ -596,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -648,13 +654,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -665,13 +671,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -682,19 +688,19 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K4" t="s">
         <v>13</v>
@@ -705,13 +711,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
@@ -722,25 +728,25 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" t="s">
         <v>57</v>
-      </c>
-      <c r="I6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J6" t="s">
-        <v>54</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -751,19 +757,19 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -774,25 +780,25 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -803,13 +809,13 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -820,19 +826,19 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -843,16 +849,19 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -863,19 +872,19 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -886,19 +895,19 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -909,13 +918,13 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K14" t="s">
         <v>23</v>
@@ -926,19 +935,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I15" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -949,19 +952,19 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I16" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -972,19 +975,19 @@
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K17" t="s">
         <v>26</v>
@@ -995,19 +998,19 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I18" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K18" t="s">
         <v>27</v>
@@ -1018,19 +1021,19 @@
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>
@@ -1041,30 +1044,53 @@
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K20" t="s">
         <v>29</v>
       </c>
     </row>
+    <row r="21" spans="2:11">
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I21" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22">
       <formula1>",Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22">
       <formula1>"SN,Program,Space Vehicle"</formula1>
     </dataValidation>
   </dataValidations>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="68">
   <si>
     <t>Plot?</t>
   </si>
@@ -187,31 +187,13 @@
     <t>Calibration</t>
   </si>
   <si>
-    <t>psia</t>
-  </si>
-  <si>
-    <t>ω</t>
-  </si>
-  <si>
-    <t>4.0</t>
-  </si>
-  <si>
-    <t>175.0</t>
-  </si>
-  <si>
-    <t>6.0</t>
+    <t>7.0</t>
   </si>
   <si>
     <t>4.8</t>
   </si>
   <si>
-    <t>140.0</t>
-  </si>
-  <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>1.5</t>
+    <t>130.0</t>
   </si>
   <si>
     <t>12.0</t>
@@ -220,13 +202,7 @@
     <t>0.99</t>
   </si>
   <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>195.0</t>
-  </si>
-  <si>
-    <t>201.0</t>
+    <t>8.1</t>
   </si>
   <si>
     <t>5.3</t>
@@ -235,16 +211,13 @@
     <t>5.5</t>
   </si>
   <si>
+    <t>1.0</t>
+  </si>
+  <si>
     <t>155.0</t>
   </si>
   <si>
-    <t>95.0</t>
-  </si>
-  <si>
     <t>1.01</t>
-  </si>
-  <si>
-    <t>1.004</t>
   </si>
 </sst>
 </file>
@@ -696,12 +669,6 @@
       <c r="F4" t="s">
         <v>52</v>
       </c>
-      <c r="H4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" t="s">
-        <v>59</v>
-      </c>
       <c r="K4" t="s">
         <v>13</v>
       </c>
@@ -736,17 +703,11 @@
       <c r="F6" t="s">
         <v>53</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>57</v>
       </c>
-      <c r="H6" t="s">
-        <v>60</v>
-      </c>
       <c r="I6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -765,12 +726,6 @@
       <c r="F7" t="s">
         <v>53</v>
       </c>
-      <c r="H7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" t="s">
-        <v>70</v>
-      </c>
       <c r="K7" t="s">
         <v>16</v>
       </c>
@@ -788,17 +743,11 @@
       <c r="F8" t="s">
         <v>53</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>58</v>
       </c>
-      <c r="H8" t="s">
-        <v>62</v>
-      </c>
       <c r="I8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -835,10 +784,10 @@
         <v>54</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -858,10 +807,10 @@
         <v>54</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -880,11 +829,8 @@
       <c r="F12" t="s">
         <v>54</v>
       </c>
-      <c r="H12" t="s">
-        <v>62</v>
-      </c>
       <c r="I12" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -904,10 +850,10 @@
         <v>54</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I13" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -960,12 +906,6 @@
       <c r="F16" t="s">
         <v>54</v>
       </c>
-      <c r="H16" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" t="s">
-        <v>66</v>
-      </c>
       <c r="K16" t="s">
         <v>25</v>
       </c>
@@ -983,12 +923,6 @@
       <c r="F17" t="s">
         <v>55</v>
       </c>
-      <c r="H17" t="s">
-        <v>65</v>
-      </c>
-      <c r="I17" t="s">
-        <v>74</v>
-      </c>
       <c r="K17" t="s">
         <v>26</v>
       </c>
@@ -1006,12 +940,6 @@
       <c r="F18" t="s">
         <v>55</v>
       </c>
-      <c r="H18" t="s">
-        <v>65</v>
-      </c>
-      <c r="I18" t="s">
-        <v>74</v>
-      </c>
       <c r="K18" t="s">
         <v>27</v>
       </c>
@@ -1030,10 +958,10 @@
         <v>55</v>
       </c>
       <c r="H19" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I19" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>
@@ -1053,10 +981,10 @@
         <v>56</v>
       </c>
       <c r="H20" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20" t="s">
         <v>67</v>
-      </c>
-      <c r="I20" t="s">
-        <v>75</v>
       </c>
       <c r="K20" t="s">
         <v>29</v>
@@ -1074,12 +1002,6 @@
       </c>
       <c r="F21" t="s">
         <v>56</v>
-      </c>
-      <c r="H21" t="s">
-        <v>68</v>
-      </c>
-      <c r="I21" t="s">
-        <v>76</v>
       </c>
       <c r="K21" t="s">
         <v>30</v>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="72">
   <si>
     <t>Plot?</t>
   </si>
@@ -109,6 +109,12 @@
     <t>LVDT-2 Status - Calibration</t>
   </si>
   <si>
+    <t>LVDT-2 Pre-Trim - Calibration</t>
+  </si>
+  <si>
+    <t>LVDT-2 Post-Trim - Calibration</t>
+  </si>
+  <si>
     <t>SN</t>
   </si>
   <si>
@@ -170,6 +176,12 @@
   </si>
   <si>
     <t>LVDT-2 Status</t>
+  </si>
+  <si>
+    <t>LVDT-2 Pre-Trim</t>
+  </si>
+  <si>
+    <t>LVDT-2 Post-Trim</t>
   </si>
   <si>
     <t>Document Profile</t>
@@ -575,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -627,13 +639,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -644,13 +656,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -661,13 +673,13 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K4" t="s">
         <v>13</v>
@@ -678,13 +690,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
@@ -695,19 +707,19 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -718,13 +730,13 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -735,19 +747,19 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -758,13 +770,13 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -775,19 +787,19 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -798,19 +810,19 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -821,16 +833,16 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -841,19 +853,19 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -864,13 +876,13 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K14" t="s">
         <v>23</v>
@@ -881,13 +893,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -898,13 +910,13 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -915,13 +927,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K17" t="s">
         <v>26</v>
@@ -932,13 +944,13 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K18" t="s">
         <v>27</v>
@@ -949,19 +961,19 @@
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H19" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I19" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>
@@ -972,19 +984,19 @@
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H20" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I20" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K20" t="s">
         <v>29</v>
@@ -995,24 +1007,58 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K21" t="s">
         <v>30</v>
       </c>
     </row>
+    <row r="22" spans="2:11">
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" t="s">
+        <v>60</v>
+      </c>
+      <c r="K22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" t="s">
+        <v>60</v>
+      </c>
+      <c r="K23" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A24">
       <formula1>",Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D24">
       <formula1>"SN,Program,Space Vehicle"</formula1>
     </dataValidation>
   </dataValidations>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
   <si>
     <t>Plot?</t>
   </si>
@@ -197,6 +197,18 @@
   </si>
   <si>
     <t>Calibration</t>
+  </si>
+  <si>
+    <t>psia</t>
+  </si>
+  <si>
+    <t>Ohm</t>
+  </si>
+  <si>
+    <t>grms</t>
+  </si>
+  <si>
+    <t>TC-01</t>
   </si>
   <si>
     <t>7.0</t>
@@ -715,11 +727,17 @@
       <c r="F6" t="s">
         <v>57</v>
       </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
       <c r="H6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" t="s">
         <v>61</v>
-      </c>
-      <c r="I6" t="s">
-        <v>66</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -755,11 +773,17 @@
       <c r="F8" t="s">
         <v>57</v>
       </c>
+      <c r="G8" t="s">
+        <v>62</v>
+      </c>
       <c r="H8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J8" t="s">
         <v>62</v>
-      </c>
-      <c r="I8" t="s">
-        <v>67</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -796,10 +820,10 @@
         <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -819,10 +843,10 @@
         <v>58</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -842,7 +866,7 @@
         <v>58</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -862,10 +886,10 @@
         <v>58</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -969,11 +993,17 @@
       <c r="F19" t="s">
         <v>59</v>
       </c>
+      <c r="G19" t="s">
+        <v>63</v>
+      </c>
       <c r="H19" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I19" t="s">
-        <v>64</v>
+        <v>68</v>
+      </c>
+      <c r="J19" t="s">
+        <v>63</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>
@@ -992,11 +1022,17 @@
       <c r="F20" t="s">
         <v>60</v>
       </c>
+      <c r="G20" t="s">
+        <v>64</v>
+      </c>
       <c r="H20" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I20" t="s">
-        <v>71</v>
+        <v>75</v>
+      </c>
+      <c r="J20" t="s">
+        <v>64</v>
       </c>
       <c r="K20" t="s">
         <v>29</v>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="74">
   <si>
     <t>Plot?</t>
   </si>
@@ -109,9 +109,6 @@
     <t>LVDT-2 Status - Calibration</t>
   </si>
   <si>
-    <t>LVDT-2 Pre-Trim - Calibration</t>
-  </si>
-  <si>
     <t>LVDT-2 Post-Trim - Calibration</t>
   </si>
   <si>
@@ -176,9 +173,6 @@
   </si>
   <si>
     <t>LVDT-2 Status</t>
-  </si>
-  <si>
-    <t>LVDT-2 Pre-Trim</t>
   </si>
   <si>
     <t>LVDT-2 Post-Trim</t>
@@ -599,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -651,13 +645,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -668,13 +662,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -685,13 +679,13 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K4" t="s">
         <v>13</v>
@@ -702,13 +696,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
@@ -719,25 +713,25 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -748,13 +742,13 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -765,25 +759,25 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -794,13 +788,13 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -811,19 +805,19 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -834,19 +828,19 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -857,16 +851,16 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -877,19 +871,19 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -900,13 +894,13 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K14" t="s">
         <v>23</v>
@@ -917,13 +911,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -934,13 +928,13 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -951,13 +945,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K17" t="s">
         <v>26</v>
@@ -968,13 +962,13 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K18" t="s">
         <v>27</v>
@@ -985,25 +979,25 @@
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>
@@ -1014,25 +1008,25 @@
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K20" t="s">
         <v>29</v>
@@ -1043,13 +1037,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K21" t="s">
         <v>30</v>
@@ -1060,41 +1054,24 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K22" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:11">
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="K23" t="s">
-        <v>32</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A23">
       <formula1>",Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D23">
       <formula1>"SN,Program,Space Vehicle"</formula1>
     </dataValidation>
   </dataValidations>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="72">
   <si>
     <t>Plot?</t>
   </si>
@@ -91,7 +91,16 @@
     <t>Power Draw Idle Source - Performance KPI</t>
   </si>
   <si>
-    <t>Thermal Margin Low - Performance KPI</t>
+    <t>Random Vib Z Amplitude - Environmental</t>
+  </si>
+  <si>
+    <t>TC-02 Post Trim - Calibration</t>
+  </si>
+  <si>
+    <t>LVDT-2 Status - Calibration</t>
+  </si>
+  <si>
+    <t>LVDT-2 Post-Trim - Calibration</t>
   </si>
   <si>
     <t>Thermal Soak High Status - Environmental</t>
@@ -100,18 +109,6 @@
     <t>Thermal Soak High Duration - Environmental</t>
   </si>
   <si>
-    <t>Random Vib Z Amplitude - Environmental</t>
-  </si>
-  <si>
-    <t>TC-02 Post Trim - Calibration</t>
-  </si>
-  <si>
-    <t>LVDT-2 Status - Calibration</t>
-  </si>
-  <si>
-    <t>LVDT-2 Post-Trim - Calibration</t>
-  </si>
-  <si>
     <t>SN</t>
   </si>
   <si>
@@ -157,25 +154,22 @@
     <t>Power Draw Idle Source</t>
   </si>
   <si>
-    <t>Thermal Margin Low</t>
+    <t>Random Vib Z Amplitude</t>
+  </si>
+  <si>
+    <t>TC-02 Post Trim</t>
+  </si>
+  <si>
+    <t>LVDT-2 Status</t>
+  </si>
+  <si>
+    <t>LVDT-2 Post-Trim</t>
   </si>
   <si>
     <t>Thermal Soak High Status</t>
   </si>
   <si>
     <t>Thermal Soak High Duration</t>
-  </si>
-  <si>
-    <t>Random Vib Z Amplitude</t>
-  </si>
-  <si>
-    <t>TC-02 Post Trim</t>
-  </si>
-  <si>
-    <t>LVDT-2 Status</t>
-  </si>
-  <si>
-    <t>LVDT-2 Post-Trim</t>
   </si>
   <si>
     <t>Document Profile</t>
@@ -593,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -645,13 +639,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="s">
-        <v>33</v>
-      </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -662,13 +656,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -679,13 +673,13 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K4" t="s">
         <v>13</v>
@@ -696,13 +690,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
@@ -713,25 +707,25 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -742,13 +736,13 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -759,25 +753,25 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -788,13 +782,13 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -805,19 +799,19 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -828,19 +822,19 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -851,16 +845,16 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -871,19 +865,19 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -894,13 +888,13 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K14" t="s">
         <v>23</v>
@@ -911,13 +905,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -928,13 +922,25 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="G16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" t="s">
+        <v>59</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -945,13 +951,25 @@
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="G17" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" t="s">
+        <v>60</v>
       </c>
       <c r="K17" t="s">
         <v>26</v>
@@ -962,13 +980,13 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K18" t="s">
         <v>27</v>
@@ -979,25 +997,13 @@
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>61</v>
-      </c>
-      <c r="H19" t="s">
-        <v>66</v>
-      </c>
-      <c r="I19" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>
@@ -1008,25 +1014,13 @@
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" t="s">
-        <v>67</v>
-      </c>
-      <c r="I20" t="s">
-        <v>73</v>
-      </c>
-      <c r="J20" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="K20" t="s">
         <v>29</v>
@@ -1037,41 +1031,24 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K21" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="2:11">
-      <c r="B22" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-      <c r="K22" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A23">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22">
       <formula1>",Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D23">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22">
       <formula1>"SN,Program,Space Vehicle"</formula1>
     </dataValidation>
   </dataValidations>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
   <si>
     <t>Plot?</t>
   </si>
@@ -109,6 +109,12 @@
     <t>Thermal Soak High Duration - Environmental</t>
   </si>
   <si>
+    <t>Thermal Margin Low - Performance KPI</t>
+  </si>
+  <si>
+    <t>LVDT-2 Pre-Trim - Calibration</t>
+  </si>
+  <si>
     <t>SN</t>
   </si>
   <si>
@@ -170,6 +176,12 @@
   </si>
   <si>
     <t>Thermal Soak High Duration</t>
+  </si>
+  <si>
+    <t>Thermal Margin Low</t>
+  </si>
+  <si>
+    <t>LVDT-2 Pre-Trim</t>
   </si>
   <si>
     <t>Document Profile</t>
@@ -587,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -639,13 +651,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -656,13 +668,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -673,13 +685,13 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K4" t="s">
         <v>13</v>
@@ -690,13 +702,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
@@ -707,25 +719,25 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" t="s">
         <v>61</v>
-      </c>
-      <c r="I6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J6" t="s">
-        <v>57</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -736,13 +748,13 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -753,25 +765,25 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J8" t="s">
         <v>62</v>
-      </c>
-      <c r="I8" t="s">
-        <v>67</v>
-      </c>
-      <c r="J8" t="s">
-        <v>58</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -782,13 +794,13 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -799,19 +811,19 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -822,19 +834,19 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -845,16 +857,16 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -865,19 +877,19 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -888,13 +900,13 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K14" t="s">
         <v>23</v>
@@ -905,13 +917,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -922,25 +934,25 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -951,25 +963,25 @@
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K17" t="s">
         <v>26</v>
@@ -980,13 +992,13 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K18" t="s">
         <v>27</v>
@@ -997,13 +1009,13 @@
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>
@@ -1014,13 +1026,13 @@
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K20" t="s">
         <v>29</v>
@@ -1031,24 +1043,58 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K21" t="s">
         <v>30</v>
       </c>
     </row>
+    <row r="22" spans="2:11">
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" t="s">
+        <v>60</v>
+      </c>
+      <c r="K23" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A24">
       <formula1>",Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D24">
       <formula1>"SN,Program,Space Vehicle"</formula1>
     </dataValidation>
   </dataValidations>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -91,6 +91,15 @@
     <t>Power Draw Idle Source - Performance KPI</t>
   </si>
   <si>
+    <t>Thermal Margin Low - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Status - Environmental</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Duration - Environmental</t>
+  </si>
+  <si>
     <t>Random Vib Z Amplitude - Environmental</t>
   </si>
   <si>
@@ -100,21 +109,12 @@
     <t>LVDT-2 Status - Calibration</t>
   </si>
   <si>
+    <t>LVDT-2 Pre-Trim - Calibration</t>
+  </si>
+  <si>
     <t>LVDT-2 Post-Trim - Calibration</t>
   </si>
   <si>
-    <t>Thermal Soak High Status - Environmental</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Duration - Environmental</t>
-  </si>
-  <si>
-    <t>Thermal Margin Low - Performance KPI</t>
-  </si>
-  <si>
-    <t>LVDT-2 Pre-Trim - Calibration</t>
-  </si>
-  <si>
     <t>SN</t>
   </si>
   <si>
@@ -160,6 +160,15 @@
     <t>Power Draw Idle Source</t>
   </si>
   <si>
+    <t>Thermal Margin Low</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Status</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Duration</t>
+  </si>
+  <si>
     <t>Random Vib Z Amplitude</t>
   </si>
   <si>
@@ -169,19 +178,10 @@
     <t>LVDT-2 Status</t>
   </si>
   <si>
+    <t>LVDT-2 Pre-Trim</t>
+  </si>
+  <si>
     <t>LVDT-2 Post-Trim</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Status</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Duration</t>
-  </si>
-  <si>
-    <t>Thermal Margin Low</t>
-  </si>
-  <si>
-    <t>LVDT-2 Pre-Trim</t>
   </si>
   <si>
     <t>Document Profile</t>
@@ -940,19 +940,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" t="s">
-        <v>68</v>
-      </c>
-      <c r="I16" t="s">
-        <v>68</v>
-      </c>
-      <c r="J16" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -969,19 +957,7 @@
         <v>49</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17" t="s">
-        <v>64</v>
-      </c>
-      <c r="H17" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" t="s">
-        <v>75</v>
-      </c>
-      <c r="J17" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K17" t="s">
         <v>26</v>
@@ -998,7 +974,7 @@
         <v>50</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K18" t="s">
         <v>27</v>
@@ -1015,7 +991,19 @@
         <v>51</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="G19" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" t="s">
+        <v>68</v>
+      </c>
+      <c r="J19" t="s">
+        <v>63</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>
@@ -1032,7 +1020,19 @@
         <v>52</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="G20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" t="s">
+        <v>75</v>
+      </c>
+      <c r="J20" t="s">
+        <v>64</v>
       </c>
       <c r="K20" t="s">
         <v>29</v>
@@ -1049,7 +1049,7 @@
         <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K21" t="s">
         <v>30</v>
@@ -1066,7 +1066,7 @@
         <v>54</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K22" t="s">
         <v>31</v>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="73">
   <si>
     <t>Plot?</t>
   </si>
@@ -49,156 +49,147 @@
     <t>Series Label</t>
   </si>
   <si>
+    <t>Chamber Pressure Over - Functional Acceptance</t>
+  </si>
+  <si>
+    <t>Chamber Pressure Units - Functional Acceptance</t>
+  </si>
+  <si>
+    <t>Harness Resistance - Functional Acceptance</t>
+  </si>
+  <si>
+    <t>Harness Resistance Quality - Functional Acceptance</t>
+  </si>
+  <si>
+    <t>LVDT-2 Post-Trim - Calibration</t>
+  </si>
+  <si>
+    <t>LVDT-2 Pre-Trim - Calibration</t>
+  </si>
+  <si>
+    <t>LVDT-2 Status - Calibration</t>
+  </si>
+  <si>
+    <t>Power Draw Idle Source - Performance KPI</t>
+  </si>
+  <si>
+    <t>Power Draw Peak - Performance KPI</t>
+  </si>
+  <si>
+    <t>Power Draw Peak Source - Performance KPI</t>
+  </si>
+  <si>
     <t>Program Name - Document Profile</t>
   </si>
   <si>
+    <t>Random Vib Z Amplitude - Environmental</t>
+  </si>
+  <si>
     <t>Serial Number - Document Profile</t>
   </si>
   <si>
-    <t>Date Compiled - Document Profile</t>
-  </si>
-  <si>
     <t>Source Bundle Path - Document Profile</t>
   </si>
   <si>
-    <t>Chamber Pressure Over - Functional Acceptance</t>
-  </si>
-  <si>
-    <t>Chamber Pressure Units - Functional Acceptance</t>
-  </si>
-  <si>
-    <t>Harness Resistance - Functional Acceptance</t>
-  </si>
-  <si>
-    <t>Harness Resistance Quality - Functional Acceptance</t>
+    <t>TC-02 Post Trim - Calibration</t>
+  </si>
+  <si>
+    <t>Thermal Margin Low - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Duration</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Status - Environmental</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Confidence - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Target - Performance KPI</t>
   </si>
   <si>
     <t>Thrust Nominal Value - Performance KPI</t>
   </si>
   <si>
-    <t>Thrust Nominal Target - Performance KPI</t>
-  </si>
-  <si>
-    <t>Thrust Nominal Confidence - Performance KPI</t>
-  </si>
-  <si>
-    <t>Power Draw Peak - Performance KPI</t>
-  </si>
-  <si>
-    <t>Power Draw Peak Source - Performance KPI</t>
-  </si>
-  <si>
-    <t>Power Draw Idle Source - Performance KPI</t>
-  </si>
-  <si>
-    <t>Thermal Margin Low - Performance KPI</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Status - Environmental</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Duration - Environmental</t>
-  </si>
-  <si>
-    <t>Random Vib Z Amplitude - Environmental</t>
-  </si>
-  <si>
-    <t>TC-02 Post Trim - Calibration</t>
-  </si>
-  <si>
-    <t>LVDT-2 Status - Calibration</t>
-  </si>
-  <si>
-    <t>LVDT-2 Pre-Trim - Calibration</t>
-  </si>
-  <si>
-    <t>LVDT-2 Post-Trim - Calibration</t>
-  </si>
-  <si>
     <t>SN</t>
   </si>
   <si>
+    <t>Chamber Pressure Over</t>
+  </si>
+  <si>
+    <t>Chamber Pressure Units</t>
+  </si>
+  <si>
+    <t>Harness Resistance</t>
+  </si>
+  <si>
+    <t>Harness Resistance Quality</t>
+  </si>
+  <si>
+    <t>LVDT-2 Post-Trim</t>
+  </si>
+  <si>
+    <t>LVDT-2 Pre-Trim</t>
+  </si>
+  <si>
+    <t>LVDT-2 Status</t>
+  </si>
+  <si>
+    <t>Power Draw Idle Source</t>
+  </si>
+  <si>
+    <t>Power Draw Peak</t>
+  </si>
+  <si>
+    <t>Power Draw Peak Source</t>
+  </si>
+  <si>
     <t>Program Name</t>
   </si>
   <si>
+    <t>Random Vib Z Amplitude</t>
+  </si>
+  <si>
     <t>Serial Number</t>
   </si>
   <si>
-    <t>Date Compiled</t>
-  </si>
-  <si>
     <t>Source Bundle Path</t>
   </si>
   <si>
-    <t>Chamber Pressure Over</t>
-  </si>
-  <si>
-    <t>Chamber Pressure Units</t>
-  </si>
-  <si>
-    <t>Harness Resistance</t>
-  </si>
-  <si>
-    <t>Harness Resistance Quality</t>
+    <t>TC-02 Post Trim</t>
+  </si>
+  <si>
+    <t>Thermal Margin Low</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Status</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Confidence</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Target</t>
   </si>
   <si>
     <t>Thrust Nominal Value</t>
   </si>
   <si>
-    <t>Thrust Nominal Target</t>
-  </si>
-  <si>
-    <t>Thrust Nominal Confidence</t>
-  </si>
-  <si>
-    <t>Power Draw Peak</t>
-  </si>
-  <si>
-    <t>Power Draw Peak Source</t>
-  </si>
-  <si>
-    <t>Power Draw Idle Source</t>
-  </si>
-  <si>
-    <t>Thermal Margin Low</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Status</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Duration</t>
-  </si>
-  <si>
-    <t>Random Vib Z Amplitude</t>
-  </si>
-  <si>
-    <t>TC-02 Post Trim</t>
-  </si>
-  <si>
-    <t>LVDT-2 Status</t>
-  </si>
-  <si>
-    <t>LVDT-2 Pre-Trim</t>
-  </si>
-  <si>
-    <t>LVDT-2 Post-Trim</t>
+    <t>Functional Acceptance</t>
+  </si>
+  <si>
+    <t>Calibration</t>
+  </si>
+  <si>
+    <t>Performance KPI</t>
   </si>
   <si>
     <t>Document Profile</t>
   </si>
   <si>
-    <t>Functional Acceptance</t>
-  </si>
-  <si>
-    <t>Performance KPI</t>
-  </si>
-  <si>
     <t>Environmental</t>
   </si>
   <si>
-    <t>Calibration</t>
-  </si>
-  <si>
     <t>psia</t>
   </si>
   <si>
@@ -232,16 +223,16 @@
     <t>5.3</t>
   </si>
   <si>
+    <t>155.0</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
     <t>5.5</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>155.0</t>
-  </si>
-  <si>
-    <t>1.01</t>
   </si>
 </sst>
 </file>
@@ -599,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -651,13 +642,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>53</v>
+      </c>
+      <c r="G2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" t="s">
+        <v>58</v>
       </c>
       <c r="K2" t="s">
         <v>11</v>
@@ -668,13 +671,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -685,13 +688,25 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>53</v>
+      </c>
+      <c r="G4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J4" t="s">
+        <v>59</v>
       </c>
       <c r="K4" t="s">
         <v>13</v>
@@ -702,13 +717,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
@@ -719,25 +734,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -748,13 +751,13 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -765,25 +768,13 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -794,13 +785,13 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
@@ -811,19 +802,19 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -834,19 +825,13 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -857,16 +842,13 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I12" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -877,19 +859,25 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="G13" t="s">
+        <v>60</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I13" t="s">
-        <v>74</v>
+        <v>65</v>
+      </c>
+      <c r="J13" t="s">
+        <v>60</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -900,13 +888,13 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K14" t="s">
         <v>23</v>
@@ -917,13 +905,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -934,13 +922,25 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>54</v>
+      </c>
+      <c r="G16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16" t="s">
+        <v>61</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -951,13 +951,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K17" t="s">
         <v>26</v>
@@ -968,13 +968,10 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="K18" t="s">
         <v>27</v>
@@ -985,25 +982,13 @@
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" t="s">
-        <v>63</v>
-      </c>
-      <c r="H19" t="s">
-        <v>68</v>
-      </c>
-      <c r="I19" t="s">
-        <v>68</v>
-      </c>
-      <c r="J19" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>
@@ -1014,25 +999,16 @@
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="I20" t="s">
-        <v>75</v>
-      </c>
-      <c r="J20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K20" t="s">
         <v>29</v>
@@ -1043,13 +1019,19 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>55</v>
+      </c>
+      <c r="H21" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" t="s">
+        <v>72</v>
       </c>
       <c r="K21" t="s">
         <v>30</v>
@@ -1060,41 +1042,30 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>55</v>
+      </c>
+      <c r="H22" t="s">
+        <v>63</v>
+      </c>
+      <c r="I22" t="s">
+        <v>72</v>
       </c>
       <c r="K22" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:11">
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="K23" t="s">
-        <v>32</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A23">
       <formula1>",Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D23">
       <formula1>"SN,Program,Space Vehicle"</formula1>
     </dataValidation>
   </dataValidations>

--- a/user_inputs/plot_terms.xlsx
+++ b/user_inputs/plot_terms.xlsx
@@ -49,6 +49,24 @@
     <t>Series Label</t>
   </si>
   <si>
+    <t>Program Name - Document Profile</t>
+  </si>
+  <si>
+    <t>Serial Number - Document Profile</t>
+  </si>
+  <si>
+    <t>Source Bundle Path - Document Profile</t>
+  </si>
+  <si>
+    <t>Random Vib Z Amplitude - Environmental</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Status - Environmental</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Duration</t>
+  </si>
+  <si>
     <t>Chamber Pressure Over - Functional Acceptance</t>
   </si>
   <si>
@@ -61,60 +79,57 @@
     <t>Harness Resistance Quality - Functional Acceptance</t>
   </si>
   <si>
+    <t>Power Draw Idle Source - Performance KPI</t>
+  </si>
+  <si>
+    <t>Power Draw Peak - Performance KPI</t>
+  </si>
+  <si>
+    <t>Power Draw Peak Source - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thermal Margin Low - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Value - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Target - Performance KPI</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Confidence - Performance KPI</t>
+  </si>
+  <si>
+    <t>LVDT-2 Pre-Trim - Calibration</t>
+  </si>
+  <si>
     <t>LVDT-2 Post-Trim - Calibration</t>
   </si>
   <si>
-    <t>LVDT-2 Pre-Trim - Calibration</t>
-  </si>
-  <si>
     <t>LVDT-2 Status - Calibration</t>
   </si>
   <si>
-    <t>Power Draw Idle Source - Performance KPI</t>
-  </si>
-  <si>
-    <t>Power Draw Peak - Performance KPI</t>
-  </si>
-  <si>
-    <t>Power Draw Peak Source - Performance KPI</t>
-  </si>
-  <si>
-    <t>Program Name - Document Profile</t>
-  </si>
-  <si>
-    <t>Random Vib Z Amplitude - Environmental</t>
-  </si>
-  <si>
-    <t>Serial Number - Document Profile</t>
-  </si>
-  <si>
-    <t>Source Bundle Path - Document Profile</t>
-  </si>
-  <si>
     <t>TC-02 Post Trim - Calibration</t>
   </si>
   <si>
-    <t>Thermal Margin Low - Performance KPI</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Duration</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Status - Environmental</t>
-  </si>
-  <si>
-    <t>Thrust Nominal Confidence - Performance KPI</t>
-  </si>
-  <si>
-    <t>Thrust Nominal Target - Performance KPI</t>
-  </si>
-  <si>
-    <t>Thrust Nominal Value - Performance KPI</t>
-  </si>
-  <si>
     <t>SN</t>
   </si>
   <si>
+    <t>Program Name</t>
+  </si>
+  <si>
+    <t>Serial Number</t>
+  </si>
+  <si>
+    <t>Source Bundle Path</t>
+  </si>
+  <si>
+    <t>Random Vib Z Amplitude</t>
+  </si>
+  <si>
+    <t>Thermal Soak High Status</t>
+  </si>
+  <si>
     <t>Chamber Pressure Over</t>
   </si>
   <si>
@@ -127,67 +142,55 @@
     <t>Harness Resistance Quality</t>
   </si>
   <si>
+    <t>Power Draw Idle Source</t>
+  </si>
+  <si>
+    <t>Power Draw Peak</t>
+  </si>
+  <si>
+    <t>Power Draw Peak Source</t>
+  </si>
+  <si>
+    <t>Thermal Margin Low</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Value</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Target</t>
+  </si>
+  <si>
+    <t>Thrust Nominal Confidence</t>
+  </si>
+  <si>
+    <t>LVDT-2 Pre-Trim</t>
+  </si>
+  <si>
     <t>LVDT-2 Post-Trim</t>
   </si>
   <si>
-    <t>LVDT-2 Pre-Trim</t>
-  </si>
-  <si>
     <t>LVDT-2 Status</t>
   </si>
   <si>
-    <t>Power Draw Idle Source</t>
-  </si>
-  <si>
-    <t>Power Draw Peak</t>
-  </si>
-  <si>
-    <t>Power Draw Peak Source</t>
-  </si>
-  <si>
-    <t>Program Name</t>
-  </si>
-  <si>
-    <t>Random Vib Z Amplitude</t>
-  </si>
-  <si>
-    <t>Serial Number</t>
-  </si>
-  <si>
-    <t>Source Bundle Path</t>
-  </si>
-  <si>
     <t>TC-02 Post Trim</t>
   </si>
   <si>
-    <t>Thermal Margin Low</t>
-  </si>
-  <si>
-    <t>Thermal Soak High Status</t>
-  </si>
-  <si>
-    <t>Thrust Nominal Confidence</t>
-  </si>
-  <si>
-    <t>Thrust Nominal Target</t>
-  </si>
-  <si>
-    <t>Thrust Nominal Value</t>
+    <t>Document Profile</t>
+  </si>
+  <si>
+    <t>Environmental</t>
   </si>
   <si>
     <t>Functional Acceptance</t>
   </si>
   <si>
+    <t>Performance KPI</t>
+  </si>
+  <si>
     <t>Calibration</t>
   </si>
   <si>
-    <t>Performance KPI</t>
-  </si>
-  <si>
-    <t>Document Profile</t>
-  </si>
-  <si>
-    <t>Environmental</t>
+    <t>grms</t>
   </si>
   <si>
     <t>psia</t>
@@ -196,12 +199,12 @@
     <t>Ohm</t>
   </si>
   <si>
-    <t>grms</t>
-  </si>
-  <si>
     <t>TC-01</t>
   </si>
   <si>
+    <t>12.0</t>
+  </si>
+  <si>
     <t>7.0</t>
   </si>
   <si>
@@ -211,9 +214,6 @@
     <t>130.0</t>
   </si>
   <si>
-    <t>12.0</t>
-  </si>
-  <si>
     <t>0.99</t>
   </si>
   <si>
@@ -226,13 +226,13 @@
     <t>155.0</t>
   </si>
   <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
     <t>1.01</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>5.5</t>
   </si>
 </sst>
 </file>
@@ -650,18 +650,6 @@
       <c r="F2" t="s">
         <v>53</v>
       </c>
-      <c r="G2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" t="s">
-        <v>58</v>
-      </c>
       <c r="K2" t="s">
         <v>11</v>
       </c>
@@ -696,18 +684,6 @@
       <c r="F4" t="s">
         <v>53</v>
       </c>
-      <c r="G4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" t="s">
-        <v>63</v>
-      </c>
-      <c r="I4" t="s">
-        <v>68</v>
-      </c>
-      <c r="J4" t="s">
-        <v>59</v>
-      </c>
       <c r="K4" t="s">
         <v>13</v>
       </c>
@@ -723,7 +699,19 @@
         <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" t="s">
+        <v>58</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
@@ -754,10 +742,7 @@
         <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -771,10 +756,22 @@
         <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" t="s">
+        <v>59</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -788,7 +785,7 @@
         <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
@@ -805,16 +802,22 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
         <v>55</v>
       </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
       <c r="H10" t="s">
         <v>64</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>68</v>
+      </c>
+      <c r="J10" t="s">
+        <v>60</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -828,7 +831,7 @@
         <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
         <v>55</v>
@@ -845,7 +848,7 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
         <v>56</v>
@@ -862,22 +865,16 @@
         <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H13" t="s">
         <v>65</v>
       </c>
       <c r="I13" t="s">
-        <v>65</v>
-      </c>
-      <c r="J13" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -891,7 +888,7 @@
         <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
         <v>56</v>
@@ -908,7 +905,7 @@
         <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
         <v>56</v>
@@ -925,22 +922,16 @@
         <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I16" t="s">
         <v>70</v>
-      </c>
-      <c r="J16" t="s">
-        <v>61</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -954,10 +945,16 @@
         <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="H17" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" t="s">
+        <v>70</v>
       </c>
       <c r="K17" t="s">
         <v>26</v>
@@ -971,7 +968,13 @@
         <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>48</v>
+      </c>
+      <c r="F18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" t="s">
+        <v>71</v>
       </c>
       <c r="K18" t="s">
         <v>27</v>
@@ -1005,10 +1008,7 @@
         <v>50</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
-      </c>
-      <c r="I20" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="K20" t="s">
         <v>29</v>
@@ -1025,13 +1025,7 @@
         <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="H21" t="s">
-        <v>63</v>
-      </c>
-      <c r="I21" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="K21" t="s">
         <v>30</v>
@@ -1048,13 +1042,19 @@
         <v>52</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="G22" t="s">
+        <v>61</v>
       </c>
       <c r="H22" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I22" t="s">
         <v>72</v>
+      </c>
+      <c r="J22" t="s">
+        <v>61</v>
       </c>
       <c r="K22" t="s">
         <v>31</v>
